--- a/daily_matches/job_matches_2026-07-28.xlsx
+++ b/daily_matches/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Docker</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fea98a47c7da3e79</t>
+          <t>https://www.indeed.com/viewjob?jk=4e92864ad72da7b0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Glue, Athena, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e71e87e20fcad6</t>
+          <t>https://www.indeed.com/viewjob?jk=d09b36193d9c21c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Data Engineer - GCP</t>
+          <t>Foundation Model Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, TensorFlow, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Mistral, Hugging Face, Prompt Engineering</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8432eda41e25a208</t>
+          <t>https://www.indeed.com/viewjob?jk=b2b7bed1ab7fd4d2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Operations Architect &amp; AWS Engineer, Life Sciences</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Norstella</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>LangChain, RAG, LLaMA, S3, EC2, Redshift, MLflow, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73033b8f87058bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=e90dd137a4ac6f19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Developer – Full Stack (Java Spring Boot, React, PostgreSQL)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Copilot, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Copilot, Redshift, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b818545ba973b739</t>
+          <t>https://www.indeed.com/viewjob?jk=38439f74465262d5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML, GenAI &amp; Python Developer - Onsite NJ</t>
+          <t>AWS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Empower AI Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05fd1e4957e7a08</t>
+          <t>https://www.indeed.com/viewjob?jk=34befeada094f827</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/ML, GenAI &amp; Python Developer - Onsite NJ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Hadoop, MongoDB, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29314a3543779c40</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3771f0c36b6f26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Forward Deployed Software Engineer (FDE)</t>
+          <t>Cloud Engineer — multi-cloud (AWS &amp; Azure), infrastructure &amp; data services</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>NeevSys</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery, PostgreSQL, MySQL</t>
+          <t>RAG, S3, Glue, Redshift, Synapse, Docker, Kubernetes, AKS, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d38e42153f6fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=61d9834a85f42798</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Early-Career Software Engineer - AI Applications</t>
+          <t>Software Developer (Emerging Careers)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RTI International</t>
+          <t>SAS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Gemini, Copilot, Prompt Engineering, FastAPI, Docker, CI/CD, Git</t>
+          <t>Generative AI, LangChain, RAG, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=430380effbdc4f04</t>
+          <t>https://www.indeed.com/viewjob?jk=fbbc04653e2ae65c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II – Java &amp; Microservices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Region 4 Education Service Center</t>
+          <t>Frost</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Redshift, CI/CD, Snowflake, Redshift, Power BI, Quicksight, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f972668b159bfe1</t>
+          <t>https://www.indeed.com/viewjob?jk=00069c988ac66fef</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Applications</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RTI International</t>
+          <t>Purple Wave Auction</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Pinecone, Prompt Engineering, Kubernetes, CI/CD, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637abe4676ad3cc2</t>
+          <t>https://www.indeed.com/viewjob?jk=f455b3604d919def</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, EC2, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51edf63fd9ce4d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed8d06b3ec8a6ad5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Avantos AI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd136a2c45725af</t>
+          <t>https://www.indeed.com/viewjob?jk=728e979a13366d12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer -Angular, Typescript, Bedrock</t>
+          <t>Applied AI/ML - Senior Associate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL</t>
+          <t>Generative AI, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, EC2, Glue, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=729151ced6fff1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf6aac4540381a5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer (NLP/LLM Focus)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Associated Press</t>
+          <t>Call Box</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, EC2, FastAPI, Kubernetes, CI/CD, Terraform</t>
+          <t>Machine Learning Engineer, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Terraform, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb5313dc1f40a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fea9b3e6393fbcc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - AI</t>
+          <t>AI/LLM Contractor — Career Transition Track (Contract-to-Hire)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Apache Airflow, CI/CD, Git, PySpark, Hadoop, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd1942c35e56392e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e154e827b526d4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - AI</t>
+          <t>Business Intelligence Data Modeler Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lowe's Home Improvement</t>
+          <t>Kirkland &amp; Ellis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Apache Airflow, CI/CD, Git, PySpark, Hadoop, Python, SQL</t>
+          <t>RAG, Synapse, Data Lake, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b404e83cdfac818</t>
+          <t>https://www.indeed.com/viewjob?jk=29badf7873509f1c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enterprise Information Architect I</t>
+          <t>Intermediate or Sr Software Developer (AI Platform &amp; Applications)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L.L. Bean, Inc.</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Freeport, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, CI/CD, Git, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6d7b7a1225dcc2</t>
+          <t>https://www.indeed.com/viewjob?jk=d1783e76eef53a01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tableau Senior Developer</t>
+          <t>Software Engineer-Infrastructure Automation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Git, Snowflake, Databricks, Tableau, Python, SQL</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d48807b7201b96c</t>
+          <t>https://www.indeed.com/viewjob?jk=15b1cccaf2f24e41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Software Engineer-Infrastructure Automation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crafty Software Solutions LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Webb City, MO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LLaMA, Mistral, Hugging Face, Prompt Engineering, PostgreSQL, Python, SQL, R, A/B Testing</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fea9ba6b2d0df02</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ec5a49bd5bcfd6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Applied AI Engineering Intern</t>
+          <t>Software Engineer-Infrastructure Automation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74afc122ce0a0583</t>
+          <t>https://www.indeed.com/viewjob?jk=ead59c7c11f57c9f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Applied AI/ML Engineer</t>
+          <t>Software Engineer-Infrastructure Automation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ursa Space Systems</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, Docker, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a1ad41c855b82c2</t>
+          <t>https://www.indeed.com/viewjob?jk=318db893b32aac76</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (AWS / DevOps)</t>
+          <t>Software Engineer III - Agentic AI, Java/Python</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Aeroflow Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Asheville, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Keras, CI/CD, Polars, Dask, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb2cdce093ffe79</t>
+          <t>https://www.indeed.com/viewjob?jk=2ce6c973e58ae99b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Crafty Software Solutions LLC</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Webb City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, FastAPI, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aff15c818708d71d</t>
+          <t>https://www.indeed.com/viewjob?jk=a3146e84d962c820</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Digital Manufacturing Engineer</t>
+          <t>Quality Assurance (QA) Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231d27901dfc5009</t>
+          <t>https://www.indeed.com/viewjob?jk=219a4743f392950f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Digital Manufacturing Engineer</t>
+          <t>Junior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tax Relief Advocates</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Git, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Synapse, MLflow, FastAPI, Docker, Snowflake, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d08b964fd274dd95</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d5cd7586eaab60</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI &amp; Security System Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, CI/CD, Snowflake, Databricks, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b6f1995bc1e02bc</t>
+          <t>https://www.indeed.com/viewjob?jk=55760e04a88682c7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Public Trust Clearance Required</t>
+          <t>Senior Data Engineer – Hadoop</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Core-CSI LLC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Synapse, Data Lake, CI/CD, PySpark, Polars, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df52133313b370b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ed3d05891aeb413c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Analyst, Finance Analytics &amp; AI - Deal Desk</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Cortex, Git, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9aa24bd5fb94fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=502f8e4e0f72f9d7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Product Marketing Engineer</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52e1afd88dcba233</t>
+          <t>https://www.indeed.com/viewjob?jk=ba0b92db58bd05b8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer III - Network Perimeter &amp; CDN</t>
+          <t>Senior AI Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358fc1e4b3ca6478</t>
+          <t>https://www.indeed.com/viewjob?jk=b6cd8290f0bbfe00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,42 +1581,602 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4852036d2a4d2871</t>
+          <t>https://www.indeed.com/viewjob?jk=9a6213243d8b65d4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e036f103bc0d5796</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Ad Platform</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Newsbreak</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Git, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a127f6e3ec3583e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Growth</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, EC2, Docker, Kubernetes, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33148c40f8537683</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c51630bf06b7015</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=014f6710fd62e266</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68fe9e7a2ac46de0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr. IT Analyst</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DOW</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Terraform, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfb5747a9d41a47e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer - All Levels</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Allen Control Systems</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1796c7426745b570</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee86247994d7ca3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Terraform, Git, NoSQL, Python, SQL, R, Java, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18c21c2bc74db3ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst | Contract | Los Angeles</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tech Holding</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=933c52f14d34334e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e19348696690f9d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sr. Strategist, CRM Analytics and Insights</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6b1f116537b1988</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Argonne National Laboratory</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Lemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>10</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=78a77c9eba2a3d3c</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1699fa0e2d2c879d</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Litera</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b7b629363ef50dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>State of Indiana</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9cb2cbb81ace469</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PEAK6</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33cdec98b4ac74be</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-28.xlsx
+++ b/daily_matches/job_matches_2026-07-28.xlsx
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer, Reconciliation &amp; Reporting</t>
+          <t>AI Strategist - Partner</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>34.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Snowflake, BigQuery, PySpark, Kafka, Hadoop</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c826fbf927fd818</t>
+          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Forward Deployed Engineer - AI SOC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Symple Lending</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Athena, Redshift, CI/CD, GitHub Actions, Git, Redshift, Kafka</t>
+          <t>Data Scientist, RAG, Copilot, BigQuery, Kinesis, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3dca5d46f438997</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data / AWS</t>
+          <t>Senior AI Engineer, AI Services</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Redshift, Terraform, Git, Databricks, Redshift, Python</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Cortex, S3, CI/CD, Git, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8515f265503b068a</t>
+          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intel Corporation</t>
+          <t>Latent Engineering Firm LTD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e82b2ad31e2db11</t>
+          <t>https://www.indeed.com/viewjob?jk=028991e683bc85f1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Early-Career Software Engineer - AI Applications</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>RTI International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, Gemini, Copilot, Prompt Engineering, FastAPI, Docker, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a40f6ae7d2456a50</t>
+          <t>https://www.indeed.com/viewjob?jk=1282439afb6acea7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - AI Applications</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>RTI International</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,129 +671,129 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1c6e8316708253c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0c8f95f194285e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Solution Engineer</t>
+          <t>Transportation Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>HNTB Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Prompt Engineering, Cortex, TensorFlow, PyTorch, Glue, Snowflake, Python</t>
+          <t>Data Scientist, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5c80444c5edd529</t>
+          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Technical Consultant - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Docker, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Data Lake, Kinesis, Git, Snowflake, Databricks, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a9fc85dfea980f</t>
+          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SDET - Functional POS Quality Engineer</t>
+          <t>Senior Software Engineer - Risk Technology</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+          <t>S3, EC2, Redshift, CI/CD, Jenkins, Git, Redshift, Kafka, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca239a19c09792d</t>
+          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data and Analytics - AI Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>WoodmenLife</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, PyTorch, S3, Kubernetes, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5de993a71d5ac47</t>
+          <t>https://www.indeed.com/viewjob?jk=d6368957231dde43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Data and Analytics - AI Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Jacobs</t>
+          <t>WoodmenLife</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Data Lake, Git, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1bf85bdd907f5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0472dd13746847f6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Ahead</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Scala</t>
+          <t>LangChain, RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f16abcd340d36a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a0ef013a2f473e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Dataplane</t>
+          <t>Sr Applied Data Scientist - Personalization (applied ML, PyTorch, RecSys)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51c893b18fd5d57c</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb051ab71d84ff7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, S3, CI/CD, GitHub Actions, Git, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b1b0e75440de2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cfab7796442687c5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Eng</t>
+          <t>SDET - Retail</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yalo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Kafka, Python, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=817c691f9abc315e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9de0aec01bb34e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SDET - Retail</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ad10f3b95a311d</t>
+          <t>https://www.indeed.com/viewjob?jk=023263d27cd1c111</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>DATA ANALYST L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MACH INDUSTRIES</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Huntington Beach, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02439a77afb5f60</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab044b8db573cc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-28.xlsx
+++ b/daily_matches/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Strategist - Partner</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34.4</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>RAG, Copilot, Glue, BigQuery, Kinesis, Dataflow, Kubernetes, Apache Airflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a3661ad61353f4f</t>
+          <t>https://www.indeed.com/viewjob?jk=806ad6cc0b86fe80</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - AI SOC</t>
+          <t>Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, BigQuery, Kinesis, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc6c1dd7963fdfd</t>
+          <t>https://www.indeed.com/viewjob?jk=f90d4db047b202c6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, AI Services</t>
+          <t>AI Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Cortex, S3, CI/CD, Git, Snowflake</t>
+          <t>AI Engineer, Data Scientist, LangChain, Hugging Face, MLflow, Kubernetes, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,164 +566,164 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9e6663fc1113d93</t>
+          <t>https://www.indeed.com/viewjob?jk=5c685db79c3a032d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Latent Engineering Firm LTD</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Kinesis, Docker, Kubernetes, AKS, Terraform, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=028991e683bc85f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1a16a037aab83b32</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Early-Career Software Engineer - AI Applications</t>
+          <t>Research Scientist II, Step 1-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RTI International</t>
+          <t>University of Alabama in Huntsville</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Gemini, Copilot, Prompt Engineering, FastAPI, Docker, CI/CD, Git</t>
+          <t>RAG, LLaMA, MLflow, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1282439afb6acea7</t>
+          <t>https://www.indeed.com/viewjob?jk=4b876b59e168c817</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer - AI Applications</t>
+          <t>Predictive Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RTI International</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Tableau, Power BI, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0c8f95f194285e</t>
+          <t>https://www.indeed.com/viewjob?jk=51782b311045d76a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Transportation Data Scientist</t>
+          <t>Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HNTB Corporation</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Synapse, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Generative AI, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62170821e4e69c98</t>
+          <t>https://www.indeed.com/viewjob?jk=1aab47487016cd9b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Data &amp; Analytics</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,29 +731,29 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Git, Snowflake, Databricks, Hadoop, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34f1952389da0adb</t>
+          <t>https://www.indeed.com/viewjob?jk=73817ca2e0647e01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Risk Technology</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,147 +766,147 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, EC2, Redshift, CI/CD, Jenkins, Git, Redshift, Kafka, SQL, R</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d2a8bd8e9419e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a9eb91521a8913</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data and Analytics - AI Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WoodmenLife</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6368957231dde43</t>
+          <t>https://www.indeed.com/viewjob?jk=3fff2ac23d5d106b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data and Analytics - AI Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WoodmenLife</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Copilot, TensorFlow, PyTorch, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0472dd13746847f6</t>
+          <t>https://www.indeed.com/viewjob?jk=7563330550f74213</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, RAG, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a0ef013a2f473e</t>
+          <t>https://www.indeed.com/viewjob?jk=98b161e9453607bf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Applied Data Scientist - Personalization (applied ML, PyTorch, RecSys)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, PyTorch, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,147 +916,2177 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb051ab71d84ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec02dc71d8b6771c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, CI/CD, GitHub Actions, Git, Kafka, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfab7796442687c5</t>
+          <t>https://www.indeed.com/viewjob?jk=67ffe670b23717f7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SDET - Retail</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9de0aec01bb34e</t>
+          <t>https://www.indeed.com/viewjob?jk=f96d14c415310a3c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=023263d27cd1c111</t>
+          <t>https://www.indeed.com/viewjob?jk=27cbf5e5a3bd0bff</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DATA ANALYST L3(CONTRACT)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a8c0f69d070c5c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4253785a5307c23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=384b0d10c55a178e</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b57204c2660d7c3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f4c8d4b49022211</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fayetteville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0c00fc4a1c17055</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Melville, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce17357fe6476d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23fb1f69a6467c7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd730aabb25cf8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Little Rock, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83e4d71c8fad9275</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=884cbec3e783fd82</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=098e1bfaa67200ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49951da88ee7e504</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1acaa85f3f1d2cf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74fc9d9c37f281a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f40fd84d395c9d69</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1683dd39b3f0af6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d6b8cd2f117f668</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfad412ca910597f</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca80711985733e5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Toledo, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dab666345e6d2f60</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30361a58fb7c2766</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31819daea38633e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef93622d2283e841</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90aac72149cfe4ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d790f859ac02ee17</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Florham Park, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c38c900de86c434c</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7af445c5fde8dce</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=944956a99542e915</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68f1b3f97129a3f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d901aab2a81a029</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d482e440287378d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1eb5bbfec5db761f</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4280c400cf4cc190</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f19fcb0af89073b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87ca4bfa9e307a80</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e18706560e0230a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3c2e0734ab5f4ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Spartanburg, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de395c2142404044</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e949d415f9fa250</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c226c4035eb8cf04</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd051b2edaf1400</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dee64afc08a9bef4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71f3993ca15d38f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=106948c1cc510841</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Rosemont, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=636fb0134269d362</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=893df4394b7a0148</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LLaMA, Mistral, Prompt Engineering, TensorFlow, NLTK, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=592bc675839e0e99</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Linux Systems Engineer - Server Migration</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb1c9201a8161c46</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa570507071a750e</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Recolabs</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=102329a8e5c5946e</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Senior AI Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>The Hartford</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=069422425deb2f92</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, Kafka, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d35911913efb4d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Frontline Education</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Kafka, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fbfe00edebebf90</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SDET - Functional POS Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Berwyn, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45d29499f51fb765</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AI Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>signitives IT Solutions</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a00f90bb7fd4f51</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - QuantumBlack, AI by McKinsey</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>McKinsey &amp; Company</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, NoSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae2d8ccff2b67768</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Git, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf24b6b2cc90d27f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior AI Python Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Select Minds LLC</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Git, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ab044b8db573cc</t>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3992cd1ba674b3ea</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-28.xlsx
+++ b/daily_matches/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, S3, CI/CD, Git, PostgreSQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, EC2, Redshift, Data Lake, Kinesis, Redshift, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58359e4adc4e423e</t>
+          <t>https://www.indeed.com/viewjob?jk=957b57fb2d35abb6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer Senior Consultant I -</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Archer Technologies</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c4ae1b70e64e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=93914ebfffd3e0fa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Architect, Software Engineering</t>
+          <t>Cloud/DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>CALIBRE Systems</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL</t>
+          <t>RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66df8cc3622ab111</t>
+          <t>https://www.indeed.com/viewjob?jk=23ea1dcc62a19705</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>Senior Engineer – ML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Albertsons</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD</t>
+          <t>LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0298490c22365fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdd3b35e197c532</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer – ML</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Albertsons</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee6148be255d369</t>
+          <t>https://www.indeed.com/viewjob?jk=1401373563ae5662</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II, Advanced Research (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Kafka, Cassandra, Python, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8fc463b1f1234a3</t>
+          <t>https://www.indeed.com/viewjob?jk=bae6de8914f99b9c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Tax Technology &amp; Controls Engineer / Technology Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>project44</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f93d9150c8d68a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2752ee14a9ac7a28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data and Analytics Architect</t>
+          <t>Senior Data Scientist/AI Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>CALIBRE Systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, Git, Snowflake, Databricks, PySpark, NoSQL, Power BI</t>
+          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fca29e64567b9a7</t>
+          <t>https://www.indeed.com/viewjob?jk=dbc5bac9bd2f42e4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EDRAY</t>
+          <t>MassMutual</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, AKS, CI/CD, Terraform, Git, Databricks, Power BI, Python, SQL</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd9bc76eb207693</t>
+          <t>https://www.indeed.com/viewjob?jk=8be352eac5e25903</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Generative AI/LLM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Visual Edge IT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, Docker, Kubernetes, Python</t>
+          <t>RAG, Copilot, Synapse, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=887758e7c310917f</t>
+          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mapleton, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Databricks, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117b1dca77eb367e</t>
+          <t>https://www.indeed.com/viewjob?jk=1e76a24f2a5a599b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>AutoSavvy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Woods Cross, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R</t>
+          <t>RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bed25e09aacecc</t>
+          <t>https://www.indeed.com/viewjob?jk=21039e2b16d29978</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Berger, Goldberg, Friedman, &amp; Perlman, P.C.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Docker, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9284488ddc64765</t>
+          <t>https://www.indeed.com/viewjob?jk=c0df2faedcda21e0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data)</t>
+          <t>Senior Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Solovis</t>
+          <t>Qualia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c802ebbce7a223a1</t>
+          <t>https://www.indeed.com/viewjob?jk=99bebc0f7af2f6dc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Deployment Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Cellebrite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, MySQL, MongoDB, SQL</t>
+          <t>Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d91881ede271802</t>
+          <t>https://www.indeed.com/viewjob?jk=5720c3514d6e6ae8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Scientist</t>
+          <t>Deployment Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Cellebrite</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, CI/CD, Python</t>
+          <t>Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e1b18dcc8cc3202</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6997a012ff973b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Google Cloud Platform (GCP) Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GLASSHOUSE SYSTEMS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, SQL, R</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f88cd142184b0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Scientist - Decision Analytics, Pro</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,462 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ce4af1dda858ff2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Azure Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35bff45218ace4eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ross Dress For Less</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=338590937e0773d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Artificial Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Park Place Technologies</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Highland Heights, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Azure ML, Synapse, CI/CD, Git, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b487cf17824a6dcd</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Analyst Databricks</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Hilton Grand Vacations</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>MLflow, CI/CD, Git, Databricks, PySpark, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79bb920959efbb9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Strongsville, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, Apache Airflow, Hadoop, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48a21bba741abb42</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Roadpass Digital</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, S3, Git, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf1de0ee38f9ad5</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI and Agentic AI Risk Management Senior Specialist</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Nubank</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8633675b9e8a6b4d</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Architect Senior</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>The University of Michigan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Git, Dask, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=223a012e2fb6f441</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Management Professional - Data Engineering - Corporate Actions</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Bloomberg</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Hugging Face, PySpark, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c3d9bc7ff773ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Rockwell Automation</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, PyTorch, Python, SQL, R, Bayesian, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03269104ff2b487f</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Solution Architect, Sr</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Entergy</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Kafka, Hadoop, Cassandra, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb30cf3f38d166f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e3611409cc0333b</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Associate Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>OCLC</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Dublin, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Matplotlib, Seaborn, Python, SQL, R, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e452409ef410a06</t>
+          <t>https://www.indeed.com/viewjob?jk=0fa625fcbfc8c8ee</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-28.xlsx
+++ b/daily_matches/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, EC2, Redshift, Data Lake, Kinesis, Redshift, Kafka, Hadoop</t>
+          <t>RAG, Copilot, S3, Glue, FastAPI, CI/CD, Terraform, Git, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957b57fb2d35abb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cba2bebe1f3a11a0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer Senior Consultant I -</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NIKE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Beaverton, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>RAG, TensorFlow, PyTorch, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93914ebfffd3e0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=ceff5d9c8c0d8bc4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud/DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CALIBRE Systems</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23ea1dcc62a19705</t>
+          <t>https://www.indeed.com/viewjob?jk=9acd7b6c90f890ed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer – ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Albertsons</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fdd3b35e197c532</t>
+          <t>https://www.indeed.com/viewjob?jk=a9e76f3094c53201</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer – ML</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Albertsons</t>
+          <t>Convey</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python</t>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1401373563ae5662</t>
+          <t>https://www.indeed.com/viewjob?jk=492012b7cd47b7f1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer II, Advanced Research (Remote)</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Kafka, Cassandra, Python, R, Java</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bae6de8914f99b9c</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2a2a8b73dd0dce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tax Technology &amp; Controls Engineer / Technology Specialist</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>IT America Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2752ee14a9ac7a28</t>
+          <t>https://www.indeed.com/viewjob?jk=84c35dbd43e40c6e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/AI Data Engineer</t>
+          <t>Sr. Java Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CALIBRE Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Jenkins, Git, Kafka, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbc5bac9bd2f42e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8c41b225ed6127d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>SAP Commerce Cloud DevOps Engineer (Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MassMutual</t>
+          <t>Signet Jewelers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Gemini, Copilot, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be352eac5e25903</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6a69621b7fab7b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer and Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visual Edge IT</t>
+          <t>BETTER WORLD BOOKS MARKETPLACE INC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, CI/CD, Git, Databricks, Power BI, Python, SQL, R</t>
+          <t>Copilot, PyTorch, XGBoost, CI/CD, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcdf98078942e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d84d40c0f777cc95</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer, AQNav</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>SandboxAQ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mapleton, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, PyTorch, S3, MLflow, Docker, AKS, CI/CD, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e76a24f2a5a599b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d054210a36a14a4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Engineer, AI Platform (PhD Required)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AutoSavvy</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Woods Cross, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21039e2b16d29978</t>
+          <t>https://www.indeed.com/viewjob?jk=de0d4906018c3485</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>(USA) Senior, Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Berger, Goldberg, Friedman, &amp; Perlman, P.C.</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Docker, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0df2faedcda21e0</t>
+          <t>https://www.indeed.com/viewjob?jk=315bd0fc30ec0b9d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer in Test</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qualia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, R, Java</t>
+          <t>AI Engineer, Glue, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99bebc0f7af2f6dc</t>
+          <t>https://www.indeed.com/viewjob?jk=89b591f23029748a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deployment Engineer</t>
+          <t>Senior Build Engineer, CI/CD Efficiency</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cellebrite</t>
+          <t>1X</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Carlos, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5720c3514d6e6ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=428a640cbb343011</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deployment Engineer</t>
+          <t>Senior AI / Full-Stack Engineer (Remote)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cellebrite</t>
+          <t>NIAIS (National Initiative for AI &amp; Security)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>FastAPI, Docker, Kubernetes, PostgreSQL, MongoDB, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,77 +1021,567 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6997a012ff973b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a58df4a75f573d5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Google Cloud Platform (GCP) Architect</t>
+          <t>Senior Software Engineer, Fullstack</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GLASSHOUSE SYSTEMS</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, BigQuery, SQL, R, Scala</t>
+          <t>S3, Athena, Docker, Kubernetes, Terraform, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6caf875ac9a26f9e</t>
+          <t>https://www.indeed.com/viewjob?jk=90007982f0e125df</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Decision Analytics, Pro</t>
+          <t>AI and Agentic AI Risk Management Senior Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Nubank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d85dfacb0d8afb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI and Agentic AI Risk Management Senior Specialist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50f214634ea6377b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Build Engineer, Automated Build &amp; Release</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Carlos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd2d8bf61e74ab5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineer - SQL &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Metronet</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, PySpark, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82b077d07704e51a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, AI Generation Engine</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SandboxAQ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Python, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2adcdd2d0f0ce24</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RS21: A Data Science and Visualization Company</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Redshift, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a873a920e8efc235</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6425271da7c3217</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II - Backend-Focused Full-Stack</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fa625fcbfc8c8ee</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5b8cf369f485ee9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Product Genius</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97a088be8d835214</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Analytics Platform</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Addepar</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Lake, CI/CD, Terraform, Databricks, PySpark, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7bc12b85366baa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Eliza</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, MLflow, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da2205f3949f2104</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sr. Analyst, Retail Data Strategy</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caa470b1389587dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7b85082871f04f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55cefc6c8694e030</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior AI Data Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ab0b200e332e5f4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-28.xlsx
+++ b/daily_matches/job_matches_2026-07-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Beghou Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, FastAPI, CI/CD, Terraform, Git, PySpark, Kafka</t>
+          <t>Data Scientist, RAG, Redshift, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cba2bebe1f3a11a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f912a249dfd587</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data / Search Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIKE</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Beaverton, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Glue, Kinesis, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
+          <t>Data Scientist, RAG, Copilot, FastAPI, Docker, AKS, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceff5d9c8c0d8bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa50a1b1f574ddb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Varda Space Industries</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9acd7b6c90f890ed</t>
+          <t>https://www.indeed.com/viewjob?jk=bde0531612b3e34f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Security Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Fidelity National Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>RAG, Prompt Engineering, Data Lake, Kubernetes, AKS, Apache Airflow, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e76f3094c53201</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f33ef82a212393</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Quality System Data Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Convey</t>
+          <t>Getinge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wayne, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Kinesis, Docker, Kubernetes, Git, Kafka, MongoDB, NoSQL</t>
+          <t>Generative AI, RAG, Copilot, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=492012b7cd47b7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=88191abd86d549d3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2a2a8b73dd0dce</t>
+          <t>https://www.indeed.com/viewjob?jk=b1e732fb300609b7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IT America Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Terraform, Git, Databricks, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c35dbd43e40c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e43053fc1953845</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Java Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Duetto Research</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Jenkins, Git, Kafka, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>RAG, S3, EC2, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c41b225ed6127d8</t>
+          <t>https://www.indeed.com/viewjob?jk=562ea561635244df</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAP Commerce Cloud DevOps Engineer (Remote)</t>
+          <t>Junior Security Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Signet Jewelers</t>
+          <t>Fidelity National Financial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gemini, Copilot, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, SQL, R</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, AKS, Apache Airflow, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6a69621b7fab7b</t>
+          <t>https://www.indeed.com/viewjob?jk=38b62aab1e8febeb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer and Analyst</t>
+          <t>Cloud Support &amp; DevOPS Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BETTER WORLD BOOKS MARKETPLACE INC</t>
+          <t>Kore.ai</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mishawaka, IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, PyTorch, XGBoost, CI/CD, Git, Snowflake, Power BI, Python, SQL, R</t>
+          <t>Generative AI, Kubernetes, AKS, CI/CD, Jenkins, PostgreSQL, MySQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84d40c0f777cc95</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0063f4f570d6eb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer, AQNav</t>
+          <t>Senior Software Engineer - Kotlin/Angular</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SandboxAQ</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mayfield Heights, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, S3, MLflow, Docker, AKS, CI/CD, GitHub Actions, Git, Python</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d054210a36a14a4</t>
+          <t>https://www.indeed.com/viewjob?jk=14d01b7892b3e626</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer, AI Platform (PhD Required)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Lumeris</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java</t>
+          <t>Generative AI, Prompt Engineering, Docker, CI/CD, Terraform, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0d4906018c3485</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4dc79d645f2ca8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>(USA) Senior, Software Engineer</t>
+          <t>Senior Software Engineer, Developer Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Kafka, SQL, R, Java</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=315bd0fc30ec0b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=50a117a6ae48a2d7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer, Developer Platform</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bot Auto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Glue, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89b591f23029748a</t>
+          <t>https://www.indeed.com/viewjob?jk=fd41201bcff26761</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Build Engineer, CI/CD Efficiency</t>
+          <t>Sr AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1X</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Hadoop, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=428a640cbb343011</t>
+          <t>https://www.indeed.com/viewjob?jk=39385e2a7475246c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AI / Full-Stack Engineer (Remote)</t>
+          <t>Founding GTM Engineer / Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NIAIS (National Initiative for AI &amp; Security)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, PostgreSQL, MongoDB, Python, SQL, R, Java, Optimization</t>
+          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a58df4a75f573d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b274a1b048f59676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Fullstack</t>
+          <t>Supply Chain Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>FormFactor, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Farmers Branch, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>S3, Athena, Docker, Kubernetes, Terraform, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90007982f0e125df</t>
+          <t>https://www.indeed.com/viewjob?jk=c1766206fe897066</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI and Agentic AI Risk Management Senior Specialist</t>
+          <t>Senior Software Engineer - AI, CoCounsel International</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nubank</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+          <t>RAG, FastAPI, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d85dfacb0d8afb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a5623e7a2c0f4fb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI and Agentic AI Risk Management Senior Specialist</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nubank</t>
+          <t>CENTRIC TITLE &amp; ESCROW</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50f214634ea6377b</t>
+          <t>https://www.indeed.com/viewjob?jk=bee184fcdf172363</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Build Engineer, Automated Build &amp; Release</t>
+          <t>Computational Biologist I, Clinical Data Mining (CDM)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1X</t>
+          <t>Memorial Sloan Kettering Cancer Center</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Carlos, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd2d8bf61e74ab5b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd0a8a57a15ded7c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer - SQL &amp; Analytics</t>
+          <t>Windows Software Engineer C# - C++</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Metronet</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Snowflake, Databricks, PySpark, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, SQL, R, Java, C++</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b077d07704e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3fc5b9dea36c1d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, AI Generation Engine</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SandboxAQ</t>
+          <t>Immersion Consulting, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Python, R, Scala, Hypothesis Testing</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2adcdd2d0f0ce24</t>
+          <t>https://www.indeed.com/viewjob?jk=6269ae04c17ffcda</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer (Integration Platforms)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, Redshift, R, Scala</t>
+          <t>Copilot, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a873a920e8efc235</t>
+          <t>https://www.indeed.com/viewjob?jk=cd8876cfdd1514de</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Internship, Charging Data Modeling, Machine Learning Engineer (Fall 2026)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Snowflake, Databricks, Python, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, Git, Hadoop, NoSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,287 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6425271da7c3217</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II - Backend-Focused Full-Stack</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Expedia Group</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e5b8cf369f485ee9</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Product Genius</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97a088be8d835214</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Analytics Platform</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Addepar</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Lake, CI/CD, Terraform, Databricks, PySpark, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7bc12b85366baa5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Eliza</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, MLflow, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da2205f3949f2104</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sr. Analyst, Retail Data Strategy</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CarMax</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=caa470b1389587dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b85082871f04f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55cefc6c8694e030</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer (contract)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Python, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab0b200e332e5f4</t>
+          <t>https://www.indeed.com/viewjob?jk=aa20355d6558fb75</t>
         </is>
       </c>
     </row>
